--- a/mlucadata.xlsx
+++ b/mlucadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mlcardoso\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/845ca001af2900fe/Investimentos/MLUCA Investimentos/_Cockpit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2202CAD-39C7-4B2C-9753-B59311AC5746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{A2202CAD-39C7-4B2C-9753-B59311AC5746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED9BE96-54FE-4018-AAEB-C3611851D819}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{810A6DE5-343E-49FE-833C-B26A46355224}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{810A6DE5-343E-49FE-833C-B26A46355224}"/>
   </bookViews>
   <sheets>
     <sheet name="upload_data" sheetId="1" r:id="rId1"/>
@@ -661,9 +661,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6">
-        <v>46162</v>
-      </c>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1233,13 +1231,13 @@
         <v>19</v>
       </c>
       <c r="C30" s="3">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D30" s="4">
-        <v>125.8496</v>
+        <v>125.36088888888888</v>
       </c>
       <c r="E30" s="4">
-        <v>125.8496</v>
+        <v>125.36088888888888</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>57</v>
@@ -1265,7 +1263,7 @@
         <v>58</v>
       </c>
       <c r="B1" s="6">
-        <v>46162</v>
+        <v>46169</v>
       </c>
     </row>
   </sheetData>

--- a/mlucadata.xlsx
+++ b/mlucadata.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/845ca001af2900fe/Investimentos/MLUCA Investimentos/_Cockpit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{A2202CAD-39C7-4B2C-9753-B59311AC5746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED9BE96-54FE-4018-AAEB-C3611851D819}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{A2202CAD-39C7-4B2C-9753-B59311AC5746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E3812B3-A2AD-4A7C-ACFB-4580AED44790}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{810A6DE5-343E-49FE-833C-B26A46355224}"/>
   </bookViews>
   <sheets>
     <sheet name="upload_data" sheetId="1" r:id="rId1"/>
     <sheet name="Controle" sheetId="2" r:id="rId2"/>
+    <sheet name="Lista" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">upload_data!$A$1:$G$30</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="135">
   <si>
     <t>Ativo</t>
   </si>
@@ -220,13 +221,241 @@
   </si>
   <si>
     <t>Atualizado em</t>
+  </si>
+  <si>
+    <t>IGLN</t>
+  </si>
+  <si>
+    <t>EXUS</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Ticker Yahoo</t>
+  </si>
+  <si>
+    <t>WSML.L</t>
+  </si>
+  <si>
+    <t>EMVL.L</t>
+  </si>
+  <si>
+    <t>IWDA.L</t>
+  </si>
+  <si>
+    <t>IFSW.L</t>
+  </si>
+  <si>
+    <t>IWQU.L</t>
+  </si>
+  <si>
+    <t>IWVL.L</t>
+  </si>
+  <si>
+    <t>ETFs_BR</t>
+  </si>
+  <si>
+    <t>LFTS11</t>
+  </si>
+  <si>
+    <t>SPXR11</t>
+  </si>
+  <si>
+    <t>B5P211</t>
+  </si>
+  <si>
+    <t>LVOL11</t>
+  </si>
+  <si>
+    <t>IB5M11</t>
+  </si>
+  <si>
+    <t>SMAC11</t>
+  </si>
+  <si>
+    <t>BOVV11</t>
+  </si>
+  <si>
+    <t>BMMT11</t>
+  </si>
+  <si>
+    <t>JURO11.SA</t>
+  </si>
+  <si>
+    <t>LFTS11.SA</t>
+  </si>
+  <si>
+    <t>SPXR11.SA</t>
+  </si>
+  <si>
+    <t>B5P211.SA</t>
+  </si>
+  <si>
+    <t>LVOL11.SA</t>
+  </si>
+  <si>
+    <t>IB5M11.SA</t>
+  </si>
+  <si>
+    <t>IRIM11.SA</t>
+  </si>
+  <si>
+    <t>DIVO11.SA</t>
+  </si>
+  <si>
+    <t>SMAC11.SA</t>
+  </si>
+  <si>
+    <t>BOVV11.SA</t>
+  </si>
+  <si>
+    <t>HASH11.SA</t>
+  </si>
+  <si>
+    <t>BMMT11.SA</t>
+  </si>
+  <si>
+    <t>PSSA3</t>
+  </si>
+  <si>
+    <t>PETR4</t>
+  </si>
+  <si>
+    <t>VVEO3.SA</t>
+  </si>
+  <si>
+    <t>EGIE3.SA</t>
+  </si>
+  <si>
+    <t>BBDC4.SA</t>
+  </si>
+  <si>
+    <t>GOAU4.SA</t>
+  </si>
+  <si>
+    <t>SUZB3.SA</t>
+  </si>
+  <si>
+    <t>KLBN11.SA</t>
+  </si>
+  <si>
+    <t>UNIP6.SA</t>
+  </si>
+  <si>
+    <t>ITSA4.SA</t>
+  </si>
+  <si>
+    <t>VALE3.SA</t>
+  </si>
+  <si>
+    <t>BBAS3.SA</t>
+  </si>
+  <si>
+    <t>ALOS3.SA</t>
+  </si>
+  <si>
+    <t>CMIG4.SA</t>
+  </si>
+  <si>
+    <t>LREN3.SA</t>
+  </si>
+  <si>
+    <t>PSSA3.SA</t>
+  </si>
+  <si>
+    <t>CXSE3.SA</t>
+  </si>
+  <si>
+    <t>BEEF3.SA</t>
+  </si>
+  <si>
+    <t>WIZC3.SA</t>
+  </si>
+  <si>
+    <t>PETR4.SA</t>
+  </si>
+  <si>
+    <t>PRIO3.SA</t>
+  </si>
+  <si>
+    <t>CSAN3.SA</t>
+  </si>
+  <si>
+    <t>Outros</t>
+  </si>
+  <si>
+    <t>USDBRL</t>
+  </si>
+  <si>
+    <t>IBOV</t>
+  </si>
+  <si>
+    <t>USDBRL=X</t>
+  </si>
+  <si>
+    <t>^BVSP</t>
+  </si>
+  <si>
+    <t>Bitcoin</t>
+  </si>
+  <si>
+    <t>AVGS</t>
+  </si>
+  <si>
+    <t>AVGS.L</t>
+  </si>
+  <si>
+    <t>IGLN.L</t>
+  </si>
+  <si>
+    <t>EXUS.L</t>
+  </si>
+  <si>
+    <t>BTC-USD</t>
+  </si>
+  <si>
+    <t>S&amp;P 500</t>
+  </si>
+  <si>
+    <t>^GSPC</t>
+  </si>
+  <si>
+    <t>Dow 30</t>
+  </si>
+  <si>
+    <t>Nasdaq</t>
+  </si>
+  <si>
+    <t>VIX</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Brent</t>
+  </si>
+  <si>
+    <t>^DJI</t>
+  </si>
+  <si>
+    <t>^IXIC</t>
+  </si>
+  <si>
+    <t>^VIX</t>
+  </si>
+  <si>
+    <t>BZ=F</t>
+  </si>
+  <si>
+    <t>GC=F</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,6 +466,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -297,6 +534,20 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -312,6 +563,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1269,4 +1524,591 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0320DC4-7E62-4D3F-87F5-0B8CEA191E17}">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+</worksheet>
 </file>